--- a/Stats Sheet/Round Gaps/RR Clash 2024.xlsx
+++ b/Stats Sheet/Round Gaps/RR Clash 2024.xlsx
@@ -268,13 +268,13 @@
     <x:t>ItsShqky</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
-  </x:si>
-  <x:si>
     <x:t>LightingMC</x:t>
   </x:si>
   <x:si>
     <x:t>Markedbooboy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>PotteryTNT</x:t>
@@ -2105,9 +2105,12 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D76" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H76" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I76" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -2122,12 +2125,9 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D77" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H77" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I77" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
